--- a/target/test-classes/vinothQaAutomation.xlsx
+++ b/target/test-classes/vinothQaAutomation.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="regforms" sheetId="1" r:id="rId1"/>
+    <sheet name="patientDetails" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
   <si>
     <t>santhoshkumar</t>
   </si>
@@ -72,6 +73,27 @@
   </si>
   <si>
     <t>TC_02</t>
+  </si>
+  <si>
+    <t>patientName</t>
+  </si>
+  <si>
+    <t>visi</t>
+  </si>
+  <si>
+    <t>vinothini</t>
+  </si>
+  <si>
+    <t>ammu</t>
+  </si>
+  <si>
+    <t>painkili</t>
+  </si>
+  <si>
+    <t>dhashwan</t>
+  </si>
+  <si>
+    <t>value</t>
   </si>
 </sst>
 </file>
@@ -487,4 +509,82 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/target/test-classes/vinothQaAutomation.xlsx
+++ b/target/test-classes/vinothQaAutomation.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="regforms" sheetId="1" r:id="rId1"/>
@@ -66,9 +66,6 @@
     <t>sandy@med.com</t>
   </si>
   <si>
-    <t>testcase_id</t>
-  </si>
-  <si>
     <t>TC_01</t>
   </si>
   <si>
@@ -94,6 +91,9 @@
   </si>
   <si>
     <t>value</t>
+  </si>
+  <si>
+    <t>TC_ID</t>
   </si>
 </sst>
 </file>
@@ -442,7 +442,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -462,7 +462,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -522,10 +522,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -533,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -541,47 +541,47 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
